--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487095_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487095_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.237</v>
+        <v>5.8249</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3946</v>
+        <v>4.7951</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8424</v>
+        <v>1.0298</v>
       </c>
       <c r="G2" t="n">
         <v>-0.6068</v>
@@ -610,13 +610,13 @@
         <v>3.8602</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.5422</v>
+        <v>-2.9543</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.7251</v>
+        <v>-1.3246</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.8171</v>
+        <v>-1.6297</v>
       </c>
       <c r="V2" t="n">
         <v>5.5259</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9744</v>
+        <v>1.793</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6558</v>
+        <v>0.9562</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3187</v>
+        <v>0.8368</v>
       </c>
       <c r="G3" t="n">
         <v>3.4495</v>
@@ -688,13 +688,13 @@
         <v>3.6672</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.5752</v>
+        <v>-2.7567</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.6657</v>
+        <v>-1.3652</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9096</v>
+        <v>-1.3914</v>
       </c>
       <c r="V3" t="n">
         <v>0.3281</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. ABU SHAMS SANCHEZ</t>
+          <t>A. SAVITSKI SAVITSKAIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.5897</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8226</v>
+        <v>3.1692</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2979</v>
+        <v>-2.5794</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0138</v>
+        <v>3.0764</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2711</v>
+        <v>4.8086</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2849</v>
+        <v>-1.7322</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7747000000000001</v>
+        <v>4.5505</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0828</v>
+        <v>4.502</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6919</v>
+        <v>0.0486</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7609</v>
+        <v>-1.4742</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3539</v>
+        <v>0.3066</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.407</v>
+        <v>-1.7808</v>
       </c>
       <c r="P4" t="n">
-        <v>0.772</v>
+        <v>2.3161</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>0.772</v>
+        <v>3.2811</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2611</v>
+        <v>-2.3045</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.238</v>
+        <v>-0.66</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0231</v>
+        <v>-1.6446</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-2.4982</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2859</v>
+        <v>0.2436</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2859</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SAVITSKI SAVITSKAIA</t>
+          <t>K. ABU SHAMS SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4896</v>
+        <v>0.4444</v>
       </c>
       <c r="E5" t="n">
-        <v>3.069</v>
+        <v>0.8226</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.5794</v>
+        <v>-0.3782</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0764</v>
+        <v>0.0138</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8086</v>
+        <v>-0.2711</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.7322</v>
+        <v>0.2849</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5505</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>4.502</v>
+        <v>0.0828</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0486</v>
+        <v>0.6919</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4742</v>
+        <v>-0.7609</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3066</v>
+        <v>-0.3539</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7808</v>
+        <v>-0.407</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3161</v>
+        <v>0.772</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.2811</v>
+        <v>0.772</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.4047</v>
+        <v>-0.3414</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7601</v>
+        <v>-0.238</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.6446</v>
+        <v>-0.1035</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.4982</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2436</v>
+        <v>0.2859</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.7418</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1595</v>
+        <v>0.4005</v>
       </c>
       <c r="E6" t="n">
         <v>0.179</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0195</v>
+        <v>0.2214</v>
       </c>
       <c r="G6" t="n">
         <v>0.7623</v>
@@ -922,13 +922,13 @@
         <v>2.5091</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5328</v>
+        <v>-1.2919</v>
       </c>
       <c r="T6" t="n">
         <v>-0.2247</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3081</v>
+        <v>-1.0672</v>
       </c>
       <c r="V6" t="n">
         <v>-0.614</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6107</v>
+        <v>-0.7972</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4325</v>
+        <v>-0.8331</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1782</v>
+        <v>0.0359</v>
       </c>
       <c r="G7" t="n">
         <v>-1.8149</v>
@@ -1000,13 +1000,13 @@
         <v>0.965</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0311</v>
+        <v>-1.2175</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1057</v>
+        <v>-0.5063</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9254</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>1.2702</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.151</v>
+        <v>-1.0707</v>
       </c>
       <c r="E8" t="n">
         <v>-0.9631</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1878</v>
+        <v>-0.1075</v>
       </c>
       <c r="G8" t="n">
         <v>-0.833</v>
@@ -1078,13 +1078,13 @@
         <v>0.386</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7039</v>
+        <v>-0.6236</v>
       </c>
       <c r="T8" t="n">
         <v>-0.3569</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.347</v>
+        <v>-0.2667</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ZHANG</t>
+          <t>G. AZANZA TERUEL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0763</v>
+        <v>-2.5831</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7832</v>
+        <v>-1.0764</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2931</v>
+        <v>-1.5067</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7924</v>
+        <v>-1.2028</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.509</v>
+        <v>-0.8186</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2835</v>
+        <v>-0.3841</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3843</v>
+        <v>-0.422</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9212</v>
+        <v>-0.5848</v>
       </c>
       <c r="L9" t="n">
-        <v>0.537</v>
+        <v>0.1628</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4082</v>
+        <v>-0.7808</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5878</v>
+        <v>-0.2338</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8204</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.579</v>
+        <v>1.158</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5347</v>
+        <v>-1.0245</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1057</v>
+        <v>-0.6544</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.429</v>
+        <v>-0.3702</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3281</v>
+        <v>-1.5138</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3281</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. AZANZA TERUEL</t>
+          <t>J. ZHANG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5831</v>
+        <v>-2.6107</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0764</v>
+        <v>-2.1837</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5067</v>
+        <v>-0.427</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2028</v>
+        <v>-1.7924</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8186</v>
+        <v>-1.509</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3841</v>
+        <v>-0.2835</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.422</v>
+        <v>-0.3843</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5848</v>
+        <v>-0.9212</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1628</v>
+        <v>0.537</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7808</v>
+        <v>-1.4082</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2338</v>
+        <v>-0.5878</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.8204</v>
       </c>
       <c r="P10" t="n">
-        <v>1.158</v>
+        <v>0.579</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>1.158</v>
+        <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0245</v>
+        <v>-1.0691</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6544</v>
+        <v>-0.5063</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3702</v>
+        <v>-0.5628</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5138</v>
+        <v>-0.3281</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3281</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MENDIVIL ODERIZ</t>
+          <t>A. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7416</v>
+        <v>-2.6155</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1517</v>
+        <v>-0.1521</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5899</v>
+        <v>-2.4633</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4423</v>
+        <v>-1.0643</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3799</v>
+        <v>-0.0175</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.0624</v>
+        <v>-1.0468</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2417</v>
+        <v>0.1235</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9472</v>
+        <v>0.0828</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2945</v>
+        <v>0.0407</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2006</v>
+        <v>-1.1878</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5673</v>
+        <v>-0.1003</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7679</v>
+        <v>-1.0875</v>
       </c>
       <c r="P11" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2221</v>
+        <v>-0.8094</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1322</v>
+        <v>-0.2756</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3543</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0422</v>
+        <v>-1.5138</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0422</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. GARCIA IBAÑEZ</t>
+          <t>J. MENDIVIL ODERIZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.896</v>
+        <v>-3.1094</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3524</v>
+        <v>-2.2518</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5436</v>
+        <v>-0.8576</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0643</v>
+        <v>-3.4423</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0175</v>
+        <v>-0.3799</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0468</v>
+        <v>-3.0624</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1235</v>
+        <v>-2.2417</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0828</v>
+        <v>-0.9472</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0407</v>
+        <v>-1.2945</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1878</v>
+        <v>-1.2006</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1003</v>
+        <v>0.5673</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0875</v>
+        <v>-1.7679</v>
       </c>
       <c r="P12" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.09</v>
+        <v>-0.5899</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4759</v>
+        <v>0.0321</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6141</v>
+        <v>-0.622</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.5138</v>
+        <v>-0.0422</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.0362</v>
+        <v>-5.9757</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.0482</v>
+        <v>-6.1483</v>
       </c>
       <c r="F13" t="n">
-        <v>0.012</v>
+        <v>0.1726</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6852</v>
@@ -1468,13 +1468,13 @@
         <v>2.3161</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.556</v>
+        <v>-1.4955</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2247</v>
+        <v>-0.3249</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3313</v>
+        <v>-1.1706</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2859</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.7097</v>
+        <v>-9.709799999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.686499999999999</v>
+        <v>-3.686399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.023000000000001</v>
+        <v>-6.023199999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.1397</v>
+        <v>-5.139699999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>6.909300000000001</v>
+        <v>6.9093</v>
       </c>
       <c r="I14" t="n">
         <v>-12.0491</v>
@@ -1522,10 +1522,10 @@
         <v>6.1348</v>
       </c>
       <c r="K14" t="n">
-        <v>6.545399999999999</v>
+        <v>6.5454</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4102000000000001</v>
+        <v>-0.4101999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-11.2748</v>
@@ -1549,25 +1549,25 @@
         <v>-16.4783</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.4047</v>
+        <v>-6.4048</v>
       </c>
       <c r="U14" t="n">
-        <v>-10.0738</v>
+        <v>-10.0737</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3281999999999999</v>
+        <v>0.3281999999999997</v>
       </c>
       <c r="W14" t="n">
         <v>7.198999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.8708</v>
+        <v>-6.870799999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7123</v>
+        <v>3.1425</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4655</v>
+        <v>2.9815</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2468</v>
+        <v>0.161</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3909</v>
+        <v>1.254</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7886</v>
+        <v>1.9623</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6022</v>
+        <v>-0.7083</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7437</v>
+        <v>1.9474</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3764</v>
+        <v>2.6236</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3674</v>
+        <v>-0.6762</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3529</v>
+        <v>-0.6934</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5878</v>
+        <v>-0.6612</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2349</v>
+        <v>-0.0321</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3511</v>
+        <v>-0.772</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8951</v>
+        <v>-2.1231</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2864</v>
+        <v>0.4904</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0451</v>
+        <v>0.0873</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2413</v>
+        <v>0.4032</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.614</v>
+        <v>2.1701</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5717</v>
+        <v>3.0699</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1857</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2343</v>
+        <v>3.0975</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1804</v>
+        <v>2.0649</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0539</v>
+        <v>1.0326</v>
       </c>
       <c r="G16" t="n">
-        <v>1.254</v>
+        <v>2.3909</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9623</v>
+        <v>0.7886</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7083</v>
+        <v>1.6022</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9474</v>
+        <v>2.7437</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6236</v>
+        <v>1.3764</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6762</v>
+        <v>1.3674</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6934</v>
+        <v>-0.3529</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6612</v>
+        <v>-0.5878</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0321</v>
+        <v>0.2349</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.772</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1231</v>
+        <v>-2.8951</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4178</v>
+        <v>2.6717</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7139</v>
+        <v>1.6446</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2961</v>
+        <v>1.0271</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1701</v>
+        <v>-0.614</v>
       </c>
       <c r="W16" t="n">
-        <v>3.0699</v>
+        <v>0.5717</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8999</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. OLIVEIRA GETE</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9612</v>
+        <v>2.1036</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4707</v>
+        <v>2.0813</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4905</v>
+        <v>0.0223</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4521</v>
+        <v>1.619</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.209</v>
+        <v>-0.9729</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6612</v>
+        <v>2.5919</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1654</v>
+        <v>1.078</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4656</v>
+        <v>-0.8591</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6998</v>
+        <v>1.9371</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7131999999999999</v>
+        <v>0.541</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6747</v>
+        <v>-0.1137</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0386</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.1231</v>
+        <v>0.193</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8602</v>
+        <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7371</v>
+        <v>1.158</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2462</v>
+        <v>0.9056</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5938</v>
+        <v>0.7403</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6524</v>
+        <v>0.1652</v>
       </c>
       <c r="V17" t="n">
         <v>-0.614</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5717</v>
+        <v>1.228</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1857</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. DORRONSORO GARCES</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8362</v>
+        <v>1.8755</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.971</v>
+        <v>0.2155</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8072</v>
+        <v>1.66</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5021</v>
+        <v>0.2284</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.3371</v>
+        <v>-0.944</v>
       </c>
       <c r="I18" t="n">
-        <v>1.835</v>
+        <v>1.1724</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.649</v>
+        <v>0.5749</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.4222</v>
+        <v>-0.2227</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7733</v>
+        <v>0.7976</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1469</v>
+        <v>-0.3464</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9149</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0617</v>
+        <v>0.3748</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3511</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1231</v>
+        <v>-3.0881</v>
       </c>
       <c r="R18" t="n">
-        <v>0.772</v>
+        <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>4.3612</v>
+        <v>2.0633</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1292</v>
+        <v>1.2149</v>
       </c>
       <c r="U18" t="n">
-        <v>1.232</v>
+        <v>0.8484</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3281</v>
+        <v>1.5138</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3281</v>
+        <v>1.5138</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.552</v>
+        <v>1.6799</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1825</v>
+        <v>1.8821</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.2022</v>
       </c>
       <c r="G19" t="n">
         <v>0.3926</v>
@@ -1936,13 +1936,13 @@
         <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7384</v>
+        <v>1.8663</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5864</v>
+        <v>1.286</v>
       </c>
       <c r="U19" t="n">
-        <v>0.152</v>
+        <v>0.5803</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3818</v>
+        <v>0.7911</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6807</v>
+        <v>0.5221</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2989</v>
+        <v>0.2689</v>
       </c>
       <c r="G20" t="n">
-        <v>1.619</v>
+        <v>0.9094</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9729</v>
+        <v>0.8994</v>
       </c>
       <c r="I20" t="n">
-        <v>2.5919</v>
+        <v>0.01</v>
       </c>
       <c r="J20" t="n">
-        <v>1.078</v>
+        <v>1.503</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8591</v>
+        <v>1.3402</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9371</v>
+        <v>0.1628</v>
       </c>
       <c r="M20" t="n">
-        <v>0.541</v>
+        <v>-0.5936</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1137</v>
+        <v>-0.4408</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6546999999999999</v>
+        <v>-0.1528</v>
       </c>
       <c r="P20" t="n">
-        <v>0.193</v>
+        <v>-0.772</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.965</v>
+        <v>-1.3511</v>
       </c>
       <c r="R20" t="n">
-        <v>1.158</v>
+        <v>0.579</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1838</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3398</v>
+        <v>0.3702</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.156</v>
+        <v>0.2835</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>A. OLIVEIRA GETE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7375</v>
+        <v>0.4244</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5221</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2154</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9094</v>
+        <v>0.4521</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8994</v>
+        <v>-0.209</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01</v>
+        <v>0.6612</v>
       </c>
       <c r="J21" t="n">
-        <v>1.503</v>
+        <v>1.1654</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3402</v>
+        <v>0.4656</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1628</v>
+        <v>0.6998</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5936</v>
+        <v>-0.7131999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4408</v>
+        <v>-0.6747</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1528</v>
+        <v>-0.0386</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.772</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3511</v>
+        <v>-3.8602</v>
       </c>
       <c r="R21" t="n">
-        <v>0.579</v>
+        <v>1.7371</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6002</v>
+        <v>2.7094</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3702</v>
+        <v>1.5924</v>
       </c>
       <c r="U21" t="n">
-        <v>0.23</v>
+        <v>1.117</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>M. DORRONSORO GARCES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1394</v>
+        <v>0.3063</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3867</v>
+        <v>-2.0726</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5261</v>
+        <v>2.3789</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2284</v>
+        <v>-1.5021</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.944</v>
+        <v>-3.3371</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1724</v>
+        <v>1.835</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5749</v>
+        <v>-1.649</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2227</v>
+        <v>-2.4222</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7976</v>
+        <v>0.7733</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3464</v>
+        <v>0.1469</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.9149</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3748</v>
+        <v>1.0617</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9301</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.0881</v>
+        <v>-2.1231</v>
       </c>
       <c r="R22" t="n">
-        <v>1.158</v>
+        <v>0.772</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3272</v>
+        <v>2.8313</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3873</v>
+        <v>2.0276</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7145</v>
+        <v>0.8037</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5138</v>
+        <v>0.3281</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5138</v>
+        <v>-0.3281</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7924</v>
+        <v>-1.3512</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5047</v>
+        <v>1.705</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2971</v>
+        <v>-3.0561</v>
       </c>
       <c r="G23" t="n">
         <v>1.1718</v>
@@ -2248,13 +2248,13 @@
         <v>0.193</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6498</v>
+        <v>1.091</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4891</v>
+        <v>0.6894</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1606</v>
+        <v>0.4015</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4559</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0526</v>
+        <v>-2.36</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6257</v>
+        <v>-2.8259</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.466</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7764</v>
@@ -2326,13 +2326,13 @@
         <v>1.3511</v>
       </c>
       <c r="S24" t="n">
-        <v>1.5031</v>
+        <v>1.1957</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6214</v>
+        <v>0.4211</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8817</v>
+        <v>0.7746</v>
       </c>
       <c r="V24" t="n">
         <v>-0.0422</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.7097</v>
+        <v>9.709600000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>6.023199999999999</v>
+        <v>6.0232</v>
       </c>
       <c r="F25" t="n">
         <v>3.6865</v>
@@ -2392,7 +2392,7 @@
         <v>-6.5454</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4103000000000001</v>
+        <v>0.4103000000000003</v>
       </c>
       <c r="P25" t="n">
         <v>-11.5805</v>
@@ -2404,13 +2404,13 @@
         <v>10.6154</v>
       </c>
       <c r="S25" t="n">
-        <v>16.4785</v>
+        <v>16.4784</v>
       </c>
       <c r="T25" t="n">
         <v>10.0738</v>
       </c>
       <c r="U25" t="n">
-        <v>6.4046</v>
+        <v>6.404500000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3280999999999998</v>
